--- a/output/pdf_financials_xlsx/SRS.xlsx
+++ b/output/pdf_financials_xlsx/SRS.xlsx
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.059057</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.059057</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.003882</v>
       </c>
     </row>
     <row r="93">
@@ -3010,7 +3010,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3390,7 +3394,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.059057</v>
       </c>

--- a/output/pdf_financials_xlsx/SRS.xlsx
+++ b/output/pdf_financials_xlsx/SRS.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.208021</v>
+        <v>0.437289</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.240225</v>
+        <v>0.636076</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.106509</v>
+        <v>0.664054</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.208021</v>
+        <v>-0.437289</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.240225</v>
+        <v>-0.636076</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.106509</v>
+        <v>-0.664054</v>
       </c>
     </row>
     <row r="12">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.322545</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019261</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.11448</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.322545</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019261</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.11448</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.478013</v>
+        <v>0.155468</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.063393</v>
+        <v>0.044132</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.163104</v>
+        <v>0.048624</v>
       </c>
     </row>
     <row r="49">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5981,17 +5981,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.437289</v>
+        <v>0.437289</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-0.636076</v>
+        <v>0.636076</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>-0.664054</v>
+        <v>0.664054</v>
       </c>
     </row>
     <row r="107">

--- a/output/pdf_financials_xlsx/SRS.xlsx
+++ b/output/pdf_financials_xlsx/SRS.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.208021</v>
+        <v>0.258271</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.240225</v>
+        <v>0.270225</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.106509</v>
+        <v>0.129009</v>
       </c>
     </row>
     <row r="8">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="111">
@@ -3493,7 +3493,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3958,7 +3962,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5737,7 +5745,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -6349,7 +6361,11 @@
           <t>Directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="n">
         <v>0.05025</v>
       </c>
